--- a/artfynd/A 24425-2026 artfynd.xlsx
+++ b/artfynd/A 24425-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132600285</v>
+        <v>132599998</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496311</v>
+        <v>496320</v>
       </c>
       <c r="R2" t="n">
-        <v>6665895</v>
+        <v>6665980</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,14 +760,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -787,27 +787,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132599210</v>
+        <v>132600126</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496395</v>
+        <v>496284</v>
       </c>
       <c r="R3" t="n">
-        <v>6665819</v>
+        <v>6666009</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,19 +872,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosöksspår grans nedre del</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -904,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132599998</v>
+        <v>132600414</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496320</v>
+        <v>496271</v>
       </c>
       <c r="R4" t="n">
-        <v>6665980</v>
+        <v>6665919</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132600126</v>
+        <v>132599210</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1042,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,59 +1051,64 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496284</v>
+        <v>496395</v>
       </c>
       <c r="R5" t="n">
-        <v>6666009</v>
+        <v>6665819</v>
       </c>
       <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosöksspår grans nedre del</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
         <v>1</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132600414</v>
+        <v>132600285</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,59 +1168,59 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496271</v>
+        <v>496311</v>
       </c>
       <c r="R6" t="n">
-        <v>6665919</v>
+        <v>6665895</v>
       </c>
       <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
         <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1237,6 +1237,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132599579</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496395</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6665819</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesträd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24425-2026 artfynd.xlsx
+++ b/artfynd/A 24425-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132599998</v>
+        <v>135169919</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496320</v>
+        <v>496376</v>
       </c>
       <c r="R2" t="n">
-        <v>6665980</v>
+        <v>6665798</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132600126</v>
+        <v>132599998</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -818,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496284</v>
+        <v>496320</v>
       </c>
       <c r="R3" t="n">
-        <v>6666009</v>
+        <v>6665980</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132600414</v>
+        <v>132600126</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
@@ -930,7 +925,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496271</v>
+        <v>496284</v>
       </c>
       <c r="R4" t="n">
-        <v>6665919</v>
+        <v>6666009</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,27 +1006,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132599210</v>
+        <v>132600414</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496395</v>
+        <v>496271</v>
       </c>
       <c r="R5" t="n">
-        <v>6665819</v>
+        <v>6665919</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,19 +1091,14 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosöksspår grans nedre del</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1128,27 +1118,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132600285</v>
+        <v>135170176</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496311</v>
+        <v>496460</v>
       </c>
       <c r="R6" t="n">
-        <v>6665895</v>
+        <v>6665790</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,29 +1188,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1240,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132599579</v>
+        <v>135170344</v>
       </c>
       <c r="B7" t="n">
-        <v>103907</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223284</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kringelbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496395</v>
+        <v>496376</v>
       </c>
       <c r="R7" t="n">
-        <v>6665819</v>
+        <v>6665798</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,27 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Naturvärdesträd</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,6 +1339,347 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132599210</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496395</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6665819</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosöksspår grans nedre del</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132600285</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496311</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6665895</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132599579</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kringelbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496395</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665819</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Naturvärdesträd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
